--- a/pocho_condition_and_roles_v02.xlsx
+++ b/pocho_condition_and_roles_v02.xlsx
@@ -2,16 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" r:id="Rb33e0f5b5831457a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大きさ" sheetId="2" r:id="R313417257aee4f34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="色" sheetId="3" r:id="R1a720e48c616485e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表情" sheetId="4" r:id="R75b20427eab44fea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装飾" sheetId="5" r:id="R354691a3171b4895"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特殊組み合わせ" sheetId="6" r:id="Re45647716df340c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確率試算" sheetId="7" r:id="Re47a1d76ccec4f38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="役図鑑" sheetId="8" r:id="Reab8f45402f84b58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="役監査" sheetId="9" r:id="R6da39d1d0f554fab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挙動条件監査" sheetId="10" r:id="Rbef551b2319e4118"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" r:id="Redab07e195c74a25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大きさ" sheetId="2" r:id="R98a7077d43ef4b26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="色" sheetId="3" r:id="R3b1155f7c837418e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表情" sheetId="4" r:id="R6b7e5f511365434a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装飾" sheetId="5" r:id="Rb1c8f35139c0476c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特殊組み合わせ" sheetId="6" r:id="Rec40620d710a4dc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確率試算" sheetId="7" r:id="Rcc5d6174951540e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="役図鑑" sheetId="8" r:id="Rdc4138566d864658"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="役監査" sheetId="9" r:id="R6e5d364f3b9c4db9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挙動条件監査" sheetId="10" r:id="R3ddfccb403c74c9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v0.1.1実装監査" sheetId="11" r:id="R2866458920e74fa1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -61,7 +62,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="18">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -148,6 +149,11 @@
         <x:fgColor rgb="FFE0E7FF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF5B5660"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -156,7 +162,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="65">
+  <x:cellXfs count="68">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -305,6 +311,11 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -597,7 +608,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbca1c4fb747f425c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R30de8114973148ac"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1961,6 +1972,453 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="67" t="str">
+        <x:v>区分</x:v>
+      </x:c>
+      <x:c r="B1" s="67" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="C1" s="67" t="str">
+        <x:v>名称/属性</x:v>
+      </x:c>
+      <x:c r="D1" s="67" t="str">
+        <x:v>状態</x:v>
+      </x:c>
+      <x:c r="E1" s="67" t="str">
+        <x:v>不足要件・理由</x:v>
+      </x:c>
+      <x:c r="F1" s="67" t="str">
+        <x:v>条件</x:v>
+      </x:c>
+      <x:c r="G1" s="67" t="str">
+        <x:v>備考</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="26" t="str">
+        <x:v>挙動条件</x:v>
+      </x:c>
+      <x:c r="B2" s="26" t="str">
+        <x:v>color-5</x:v>
+      </x:c>
+      <x:c r="C2" s="26" t="str">
+        <x:v>さくら</x:v>
+      </x:c>
+      <x:c r="D2" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E2" s="26" t="str">
+        <x:v>接触継続時間の計測が未実装</x:v>
+      </x:c>
+      <x:c r="F2" s="26" t="str">
+        <x:v>相手とのサイズ差が小さい ＋ 直前に別のぽちょへ触れていない ＋ 接触時間が一定以上</x:v>
+      </x:c>
+      <x:c r="G2" s="26" t="str">
+        <x:v>color / STICK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="26" t="str">
+        <x:v>挙動条件</x:v>
+      </x:c>
+      <x:c r="B3" s="26" t="str">
+        <x:v>color-45</x:v>
+      </x:c>
+      <x:c r="C3" s="26" t="str">
+        <x:v>わかば</x:v>
+      </x:c>
+      <x:c r="D3" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E3" s="26" t="str">
+        <x:v>仕様上未実装</x:v>
+      </x:c>
+      <x:c r="F3" s="26" t="str">
+        <x:v>サイズが一度変化した履歴あり ＋ 同色相手 ＋ 高速接触</x:v>
+      </x:c>
+      <x:c r="G3" s="26" t="str">
+        <x:v>color / POP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="26" t="str">
+        <x:v>挙動条件</x:v>
+      </x:c>
+      <x:c r="B4" s="26" t="str">
+        <x:v>expression-4</x:v>
+      </x:c>
+      <x:c r="C4" s="26" t="str">
+        <x:v>ごきげん</x:v>
+      </x:c>
+      <x:c r="D4" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E4" s="26" t="str">
+        <x:v>衝突後の速度低下を接触開始時点では正確に判定できない</x:v>
+      </x:c>
+      <x:c r="F4" s="26" t="str">
+        <x:v>自分がごきげん ＋ 相手と過去に一度接触済み ＋ 今回が再接触 ＋ 接触後の速度が低下する</x:v>
+      </x:c>
+      <x:c r="G4" s="26" t="str">
+        <x:v>expression / STICK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="26" t="str">
+        <x:v>挙動条件</x:v>
+      </x:c>
+      <x:c r="B5" s="26" t="str">
+        <x:v>expression-5</x:v>
+      </x:c>
+      <x:c r="C5" s="26" t="str">
+        <x:v>ごきげん</x:v>
+      </x:c>
+      <x:c r="D5" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E5" s="26" t="str">
+        <x:v>接触継続時間の計測が未実装</x:v>
+      </x:c>
+      <x:c r="F5" s="26" t="str">
+        <x:v>自分がごきげん ＋ 相手が単独状態 ＋ 自分も単独状態 ＋ 接触時間が一定以上</x:v>
+      </x:c>
+      <x:c r="G5" s="26" t="str">
+        <x:v>expression / STICK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="26" t="str">
+        <x:v>挙動条件</x:v>
+      </x:c>
+      <x:c r="B6" s="26" t="str">
+        <x:v>expression-29</x:v>
+      </x:c>
+      <x:c r="C6" s="26" t="str">
+        <x:v>不機嫌</x:v>
+      </x:c>
+      <x:c r="D6" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E6" s="26" t="str">
+        <x:v>接触継続時間の計測が未実装</x:v>
+      </x:c>
+      <x:c r="F6" s="26" t="str">
+        <x:v>自分が不機嫌 ＋ 周囲に同表情が2体以上いる ＋ 相手が単独状態 ＋ 接触時間が一定以上</x:v>
+      </x:c>
+      <x:c r="G6" s="26" t="str">
+        <x:v>expression / STICK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="26" t="str">
+        <x:v>挙動条件</x:v>
+      </x:c>
+      <x:c r="B7" s="26" t="str">
+        <x:v>expression-35</x:v>
+      </x:c>
+      <x:c r="C7" s="26" t="str">
+        <x:v>不機嫌</x:v>
+      </x:c>
+      <x:c r="D7" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E7" s="26" t="str">
+        <x:v>衝突後に第三者を押したかの事後判定が未実装</x:v>
+      </x:c>
+      <x:c r="F7" s="26" t="str">
+        <x:v>自分が不機嫌 ＋ 周囲に他ぽちょが多い ＋ 接触地点が密集地帯 ＋ 衝突後に誰かを押す</x:v>
+      </x:c>
+      <x:c r="G7" s="26" t="str">
+        <x:v>expression / POP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="26" t="str">
+        <x:v>挙動条件</x:v>
+      </x:c>
+      <x:c r="B8" s="26" t="str">
+        <x:v>decoration-5</x:v>
+      </x:c>
+      <x:c r="C8" s="26" t="str">
+        <x:v>リボン</x:v>
+      </x:c>
+      <x:c r="D8" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E8" s="26" t="str">
+        <x:v>接触継続時間の計測が未実装</x:v>
+      </x:c>
+      <x:c r="F8" s="26" t="str">
+        <x:v>リボン付き ＋ 相手がごきげん ＋ 自分が異色 ＋ 接触前に一定時間誰とも触れていない ＋ 接触時間が一定以上</x:v>
+      </x:c>
+      <x:c r="G8" s="26" t="str">
+        <x:v>decoration / STICK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="26" t="str">
+        <x:v>挙動条件</x:v>
+      </x:c>
+      <x:c r="B9" s="26" t="str">
+        <x:v>decoration-43</x:v>
+      </x:c>
+      <x:c r="C9" s="26" t="str">
+        <x:v>芽</x:v>
+      </x:c>
+      <x:c r="D9" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E9" s="26" t="str">
+        <x:v>長時間静止後の「初めての高速移動」履歴が未実装</x:v>
+      </x:c>
+      <x:c r="F9" s="26" t="str">
+        <x:v>芽付き ＋ 長時間静止状態を経験 ＋ その後初めての高速移動 ＋ 他ぽちょへ衝突 ＋ サイズ差が大きい</x:v>
+      </x:c>
+      <x:c r="G9" s="26" t="str">
+        <x:v>decoration / POP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="26" t="str">
+        <x:v>役</x:v>
+      </x:c>
+      <x:c r="B10" s="26" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C10" s="26" t="str">
+        <x:v>すれ違い</x:v>
+      </x:c>
+      <x:c r="D10" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E10" s="26" t="str">
+        <x:v>接触継続時間の計測が未実装</x:v>
+      </x:c>
+      <x:c r="F10" s="26" t="str">
+        <x:v>相対速度が高い ＋ 接触時間が短い</x:v>
+      </x:c>
+      <x:c r="G10" s="26" t="str">
+        <x:v>★1 / 何も起こらない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="26" t="str">
+        <x:v>役</x:v>
+      </x:c>
+      <x:c r="B11" s="26" t="str">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C11" s="26" t="str">
+        <x:v>正面突破失敗</x:v>
+      </x:c>
+      <x:c r="D11" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E11" s="26" t="str">
+        <x:v>現状成立不可</x:v>
+      </x:c>
+      <x:c r="F11" s="26" t="str">
+        <x:v>両方高速 ＋ 正面衝突 ＋ 両方大サイズ ＋ 異色 ＋ どちらも弾けない</x:v>
+      </x:c>
+      <x:c r="G11" s="26" t="str">
+        <x:v>★3 / 何も起こらない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="26" t="str">
+        <x:v>役</x:v>
+      </x:c>
+      <x:c r="B12" s="26" t="str">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C12" s="26" t="str">
+        <x:v>完璧な不発</x:v>
+      </x:c>
+      <x:c r="D12" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E12" s="26" t="str">
+        <x:v>現状成立不可</x:v>
+      </x:c>
+      <x:c r="F12" s="26" t="str">
+        <x:v>高速正面衝突 ＋ 両方大 ＋ 両方不機嫌 ＋ 壁反射直後 ＋ 装飾ありを含む ＋ 周囲に4体以上 ＋ 何も起きない</x:v>
+      </x:c>
+      <x:c r="G12" s="26" t="str">
+        <x:v>★4 / 何も起こらない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="26" t="str">
+        <x:v>役</x:v>
+      </x:c>
+      <x:c r="B13" s="26" t="str">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C13" s="26" t="str">
+        <x:v>生還</x:v>
+      </x:c>
+      <x:c r="D13" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E13" s="26" t="str">
+        <x:v>条件文要修正</x:v>
+      </x:c>
+      <x:c r="F13" s="26" t="str">
+        <x:v>起爆条件候補を過去に複数回満たした履歴 ＋ 接触回数10回以上 ＋ 高速衝突 ＋ 相手が不機嫌 ＋ 天井付近 ＋ 装飾持ち ＋ それでも生存</x:v>
+      </x:c>
+      <x:c r="G13" s="26" t="str">
+        <x:v>★4 / 何も起こらない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="26" t="str">
+        <x:v>役</x:v>
+      </x:c>
+      <x:c r="B14" s="26" t="str">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C14" s="26" t="str">
+        <x:v>何も起こらない奇跡</x:v>
+      </x:c>
+      <x:c r="D14" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E14" s="26" t="str">
+        <x:v>現状成立不可</x:v>
+      </x:c>
+      <x:c r="F14" s="26" t="str">
+        <x:v>両方装飾あり ＋ 高速正面衝突 ＋ 大サイズ同士 ＋ 不機嫌同士 ＋ 双方壁3回以上 ＋ 双方天井接触済み ＋ 過去接触あり ＋ 周囲に5体以上 ＋ どの挙動条件にも該当しない</x:v>
+      </x:c>
+      <x:c r="G14" s="26" t="str">
+        <x:v>★5 / 何も起こらない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="26" t="str">
+        <x:v>役</x:v>
+      </x:c>
+      <x:c r="B15" s="26" t="str">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="str">
+        <x:v>みんな違ってみんないい</x:v>
+      </x:c>
+      <x:c r="D15" s="26" t="str">
+        <x:v>未実装</x:v>
+      </x:c>
+      <x:c r="E15" s="26" t="str">
+        <x:v>要仕様定義</x:v>
+      </x:c>
+      <x:c r="F15" s="26" t="str">
+        <x:v>誘爆込み6体 ＋ 6色全て1体ずつ ＋ 表情3種が2体ずつ ＋ 小中大が2体ずつ ＋ 装飾ありが2体以上 ＋ 同じ装飾なし ＋ 起爆ぽちょが装飾なし ＋ 全員異なる射出順区分</x:v>
+      </x:c>
+      <x:c r="G15" s="26" t="str">
+        <x:v>★5 / 弾ける</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="26" t="str">
+        <x:v>修正済み</x:v>
+      </x:c>
+      <x:c r="B16" s="26" t="str">
+        <x:v>UI-01</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="str">
+        <x:v>確認ダイアログ「やめる」</x:v>
+      </x:c>
+      <x:c r="D16" s="26" t="str">
+        <x:v>修正済み</x:v>
+      </x:c>
+      <x:c r="E16" s="26" t="str">
+        <x:v>確認キャンセル後に一時停止のまま復帰不能</x:v>
+      </x:c>
+      <x:c r="F16" s="26" t="str"/>
+      <x:c r="G16" s="26" t="str">
+        <x:v>設定画面へ戻るよう修正</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="26" t="str">
+        <x:v>修正済み</x:v>
+      </x:c>
+      <x:c r="B17" s="26" t="str">
+        <x:v>SAVE-01</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="str">
+        <x:v>リタイア/リトライ時の統計保存</x:v>
+      </x:c>
+      <x:c r="D17" s="26" t="str">
+        <x:v>修正済み</x:v>
+      </x:c>
+      <x:c r="E17" s="26" t="str">
+        <x:v>得点前に終了すると統計保存が遅れる場合</x:v>
+      </x:c>
+      <x:c r="F17" s="26" t="str"/>
+      <x:c r="G17" s="26" t="str">
+        <x:v>stopGame時にpersist</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="26" t="str">
+        <x:v>修正済み</x:v>
+      </x:c>
+      <x:c r="B18" s="26" t="str">
+        <x:v>RULE-01</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="str">
+        <x:v>直前接触/第三者押し履歴</x:v>
+      </x:c>
+      <x:c r="D18" s="26" t="str">
+        <x:v>修正済み</x:v>
+      </x:c>
+      <x:c r="E18" s="26" t="str">
+        <x:v>現在接触で履歴を先に上書きしていた</x:v>
+      </x:c>
+      <x:c r="F18" s="26" t="str"/>
+      <x:c r="G18" s="26" t="str">
+        <x:v>判定前履歴をcontextへ保持</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="26" t="str">
+        <x:v>修正済み</x:v>
+      </x:c>
+      <x:c r="B19" s="26" t="str">
+        <x:v>BOOK-01</x:v>
+      </x:c>
+      <x:c r="C19" s="26" t="str">
+        <x:v>未実装役の図鑑表示</x:v>
+      </x:c>
+      <x:c r="D19" s="26" t="str">
+        <x:v>修正済み</x:v>
+      </x:c>
+      <x:c r="E19" s="26" t="str">
+        <x:v>未実装役も図鑑に表示されていた</x:v>
+      </x:c>
+      <x:c r="F19" s="26" t="str"/>
+      <x:c r="G19" s="26" t="str">
+        <x:v>active役のみ表示</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -5833,7 +6291,7 @@
     <x:mergeCell ref="J12:K16"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b4b5426a5ca436f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3826b2ea8d14507"/>
 </x:worksheet>
 </file>
 
